--- a/simulations/phenol_hydrogen_peroxide/economics_phenol_H2O2.xlsx
+++ b/simulations/phenol_hydrogen_peroxide/economics_phenol_H2O2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\phenol_hydrogen_peroxide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10970A62-E1B4-42F4-90AA-FD626E03D42E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C347D1-63FC-4993-86C3-0367D798B0B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="131">
   <si>
     <t>Cost factors</t>
   </si>
@@ -594,9 +594,6 @@
   </si>
   <si>
     <t>Green</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>Hydrogen peroxide fossil</t>
@@ -2379,7 +2376,7 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>31</v>
@@ -2416,7 +2413,7 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>31</v>
@@ -2444,11 +2441,11 @@
       <c r="K8" s="40">
         <v>1859</v>
       </c>
-      <c r="L8" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="M8" s="40" t="s">
-        <v>129</v>
+      <c r="L8" s="40">
+        <v>1643</v>
+      </c>
+      <c r="M8" s="40">
+        <v>1675</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
@@ -2468,11 +2465,11 @@
       <c r="K9" s="40">
         <v>1997</v>
       </c>
-      <c r="L9" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="M9" s="40" t="s">
-        <v>129</v>
+      <c r="L9" s="40">
+        <v>1782</v>
+      </c>
+      <c r="M9" s="40">
+        <v>1820</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">

--- a/simulations/phenol_hydrogen_peroxide/economics_phenol_H2O2.xlsx
+++ b/simulations/phenol_hydrogen_peroxide/economics_phenol_H2O2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\phenol_hydrogen_peroxide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C347D1-63FC-4993-86C3-0367D798B0B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201DB101-E54E-41BF-B58B-BDB4275BBD8F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -760,7 +760,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -904,6 +904,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2385,15 +2388,15 @@
         <v>17.964809169999999</v>
       </c>
       <c r="E7" s="40">
-        <v>1638.9388786333618</v>
+        <v>1602</v>
       </c>
       <c r="F7" s="40">
         <f>D7*E7</f>
-        <v>29443.224195942134</v>
+        <v>28779.624290339998</v>
       </c>
       <c r="G7" s="11">
         <f>F7/Summary!$C$23</f>
-        <v>0.78507417812944269</v>
+        <v>0.76737994916082408</v>
       </c>
       <c r="I7" s="47" t="s">
         <v>126</v>
@@ -2441,7 +2444,7 @@
       <c r="K8" s="40">
         <v>1859</v>
       </c>
-      <c r="L8" s="40">
+      <c r="L8" s="61">
         <v>1643</v>
       </c>
       <c r="M8" s="40">
@@ -2465,7 +2468,7 @@
       <c r="K9" s="40">
         <v>1997</v>
       </c>
-      <c r="L9" s="40">
+      <c r="L9" s="61">
         <v>1782</v>
       </c>
       <c r="M9" s="40">
@@ -2504,7 +2507,7 @@
         <v>1926.3006830625418</v>
       </c>
       <c r="L10" s="40">
-        <v>1671.5562972717923</v>
+        <v>1602</v>
       </c>
       <c r="M10" s="40">
         <v>1747.8293363730425</v>
@@ -2567,7 +2570,7 @@
       <c r="E13" s="19"/>
       <c r="F13" s="19">
         <f>(F5+F6+F7+F10+F11)/1000000*8000</f>
-        <v>470.35454698893557</v>
+        <v>465.04574774411844</v>
       </c>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
@@ -2930,7 +2933,7 @@
       </c>
       <c r="C20" s="17">
         <f>OPEX!F13</f>
-        <v>470.35454698893557</v>
+        <v>465.04574774411844</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>85</v>
@@ -2946,7 +2949,7 @@
       </c>
       <c r="C21" s="17">
         <f>(C18+C19+C20)</f>
-        <v>490.07721021138053</v>
+        <v>484.76841096656341</v>
       </c>
       <c r="F21" s="13" t="s">
         <v>94</v>
@@ -2962,7 +2965,7 @@
       </c>
       <c r="C22" s="17">
         <f>(C21)*1000000/8000</f>
-        <v>61259.65127642257</v>
+        <v>60596.051370820423</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>93</v>
@@ -2993,7 +2996,7 @@
       </c>
       <c r="C24" s="42">
         <f>C22/C23</f>
-        <v>1.6334274418547525</v>
+        <v>1.6157332128861337</v>
       </c>
       <c r="F24" s="29" t="s">
         <v>105</v>
